--- a/stories/arbres/ATOM-SEC.RUE.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aïcha marche avec papa. Ils vont à l'école. Le cartable est sur son dos. Ils sentent le pain de la rue. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Aïcha s'arrête aussi. S'arrêter, c'est le geste. Les pieds d'Aïcha sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Papa dit : on s'arrête. Pieds au bord. Sur le trottoir. Aïcha regarde papa. Elle pose les pieds au bord. Les pieds sont calmes. Parce qu'elle s'arrête, elle attend avec papa. Papa sourit. Papa dit : bravo Aïcha. On s'arrête au trottoir. On attend avec papa. Parce que les pieds restent au bord, Aïcha est avec papa. Les pieds restent au bord du trottoir.</t>
+          <t>Aïcha marche avec papa. Ils vont à l'école. Le cartable est sur son dos. Ils sentent le pain de la rue. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Aïcha s'arrête aussi. S'arrêter, c'est le geste. Les pieds d'Aïcha sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. On s'arrête. Pieds au bord. Sur le trottoir. Aïcha regarde papa. Elle pose les pieds au bord. Les pieds sont calmes. Parce qu'elle s'arrête, elle attend avec papa. Papa sourit. Bravo Aïcha. On s'arrête au trottoir. On attend avec papa. Parce que les pieds restent au bord, Aïcha est avec papa. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aïcha marche avec papa. Ils vont à l'école. Le cartable est sur son dos. Ils sentent le pain de la rue. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Aïcha s'arrête aussi. S'arrêter, c'est le geste. Les pieds d'Aïcha sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir.
+papa|On s'arrête. Pieds au bord. Sur le trottoir.
+narrateur|Aïcha regarde papa. Elle pose les pieds au bord. Les pieds sont calmes. Parce qu'elle s'arrête, elle attend avec papa. Papa sourit.
+papa|Bravo Aïcha. On s'arrête au trottoir. On attend avec papa. Parce que les pieds restent au bord, Aïcha est avec papa.
+narrateur|Les pieds restent au bord du trottoir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Aïcha arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Aïcha s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1842,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Aïcha donne la main à papa. Ils attendent un moment.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2009,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2049,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Aïcha arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1687,7 @@
           <t>narrateur|Aïcha s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1847,6 +1859,7 @@
           <t>narrateur|Aïcha donne la main à papa. Ils attendent un moment.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2014,6 +2027,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2070,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2285,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aïcha s'arrête au trottoir</t>
+          <t>Le cartable bleu de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le cartable bleu pend au crochet. Mila et papa vont à l'école. Au bord, Mila s'arrête. Pieds au bord, sur le trottoir. Parce qu'elle s'arrête, elle attend avec papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aïcha marche avec papa. Ils vont à l'école. Le cartable est sur son dos. Ils sentent le pain de la rue. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Aïcha s'arrête aussi. S'arrêter, c'est le geste. Les pieds d'Aïcha sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. On s'arrête. Pieds au bord. Sur le trottoir. Aïcha regarde papa. Elle pose les pieds au bord. Les pieds sont calmes. Parce qu'elle s'arrête, elle attend avec papa. Papa sourit. Bravo Aïcha. On s'arrête au trottoir. On attend avec papa. Parce que les pieds restent au bord, Aïcha est avec papa. Les pieds restent au bord du trottoir.</t>
+          <t>Le cartable bleu pend au crochet. La boucle métallique fait un petit clic. Un carré de lumière pose sur le plancher. Il est jaune, un peu poussiéreux. Les chaussures de Mila attendent près du tapis. Le tapis est rêche sous les orteils. Dehors, un merle chante sur le mur. Mila vit ici, avec papa. Papa, le cartable brille ! Oui. On va à l'école. Tu mets tes chaussures ? En ce moment, Mila s'accroupit. Elle enfile la chaussure gauche. Puis la chaussure droite. Tu as fini tes chaussures ? Oui, papa. Bravo. On met le cartable. Papa aide pour la sangle. La sangle est lisse et froide. Papa ouvre la porte. L'air sent le pain de la rue. Ça sent bon ! Oui. On marche sur le trottoir. Mila donne la main à papa. Le cartable tape doucement dans le dos. Le merle chante encore, plus loin. Les pierres du trottoir sont un peu froides. L'école est près ? Bientôt. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris, bien droit. On va s'arrêter. Pieds au bord. Sur le trottoir. Mila s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Parce qu'elle s'arrête, elle attend. Une voiture passe au loin. Mila serre la main de papa. Bravo, Mila. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aïcha marche avec papa. Ils vont à l'école. Le cartable est sur son dos. Ils sentent le pain de la rue. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Aïcha s'arrête aussi. S'arrêter, c'est le geste. Les pieds d'Aïcha sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir.
-papa|On s'arrête. Pieds au bord. Sur le trottoir.
-narrateur|Aïcha regarde papa. Elle pose les pieds au bord. Les pieds sont calmes. Parce qu'elle s'arrête, elle attend avec papa. Papa sourit.
-papa|Bravo Aïcha. On s'arrête au trottoir. On attend avec papa. Parce que les pieds restent au bord, Aïcha est avec papa.
+          <t>narrateur|Le cartable bleu pend au crochet.
+narrateur|La boucle métallique fait un petit clic.
+narrateur|Un carré de lumière pose sur le plancher.
+narrateur|Il est jaune, un peu poussiéreux.
+narrateur|Les chaussures de Mila attendent près du tapis.
+narrateur|Le tapis est rêche sous les orteils.
+narrateur|Dehors, un merle chante sur le mur.
+narrateur|Mila vit ici, avec papa.
+enfant-f|Papa, le cartable brille !
+papa|Oui.
+papa|On va à l'école.
+papa|Tu mets tes chaussures ?
+narrateur|En ce moment, Mila s'accroupit.
+narrateur|Elle enfile la chaussure gauche.
+narrateur|Puis la chaussure droite.
+papa|Tu as fini tes chaussures ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|On met le cartable.
+narrateur|Papa aide pour la sangle.
+narrateur|La sangle est lisse et froide.
+narrateur|Papa ouvre la porte.
+narrateur|L'air sent le pain de la rue.
+enfant-f|Ça sent bon !
+papa|Oui.
+papa|On marche sur le trottoir.
+narrateur|Mila donne la main à papa.
+narrateur|Le cartable tape doucement dans le dos.
+narrateur|Le merle chante encore, plus loin.
+narrateur|Les pierres du trottoir sont un peu froides.
+enfant-f|L'école est près ?
+papa|Bientôt.
+papa|On reste sur le trottoir.
+narrateur|Le bord du trottoir arrive.
+narrateur|Le bord est gris, bien droit.
+papa|On va s'arrêter.
+papa|Pieds au bord.
+papa|Sur le trottoir.
+narrateur|Mila s'arrête.
+narrateur|Ses pieds sont au bord.
+narrateur|Les pieds restent au bord.
+narrateur|Les pieds sont sur le trottoir.
+enfant-f|Je m'arrête.
+papa|Oui.
+papa|On attend avec papa.
+papa|Tes pieds sont calmes ?
+enfant-f|Oui.
+narrateur|Parce qu'elle s'arrête, elle attend.
+narrateur|Une voiture passe au loin.
+narrateur|Mila serre la main de papa.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>voiture_passe</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1408,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aïcha arrive au bord. Que fait-elle ?</t>
+          <t>Mila arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1568,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Aïcha arrive au bord. Que fait-elle ?</t>
+          <t>narrateur|Mila arrive au bord.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1597,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aïcha s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+          <t>Mila s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Mila. On attend avec papa. Parce que les pieds restent au bord, Mila attend. La sangle du cartable est froide. La main de papa est chaude.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1684,7 +1745,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Aïcha s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+          <t>narrateur|Mila s'arrête au bord.
+narrateur|Les pieds sont sur le trottoir.
+narrateur|Les pieds restent au bord.
+papa|Tu t'arrêtes au trottoir ?
+enfant-f|Oui.
+enfant-f|Je m'arrête.
+papa|Bravo, Mila.
+papa|On attend avec papa.
+narrateur|Parce que les pieds restent au bord, Mila attend.
+narrateur|La sangle du cartable est froide.
+narrateur|La main de papa est chaude.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1712,7 +1783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Aïcha donne la main à papa. Ils attendent un moment.</t>
+          <t>On y va ensemble ? Oui, papa. Ils marchent avec l'adulte. Le portail de l'école est bleu. Il sent le métal froid. Tu donnes le cartable ? Mila pousse la sangle. Il est prêt. Tu as fini ? Oui. Bravo. Le merle chante encore sur le mur. Le carré de lumière reste loin, à la maison.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1856,7 +1927,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Aïcha donne la main à papa. Ils attendent un moment.</t>
+          <t>papa|On y va ensemble ?
+enfant-f|Oui, papa.
+narrateur|Ils marchent avec l'adulte.
+narrateur|Le portail de l'école est bleu.
+narrateur|Il sent le métal froid.
+papa|Tu donnes le cartable ?
+narrateur|Mila pousse la sangle.
+enfant-f|Il est prêt.
+papa|Tu as fini ?
+enfant-f|Oui.
+papa|Bravo.
+narrateur|Le merle chante encore sur le mur.
+narrateur|Le carré de lumière reste loin, à la maison.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1884,7 +1967,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je me suis arrêtée. Pieds au bord. Sur le trottoir. Bravo, Mila. Le cartable bleu tape encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2024,7 +2107,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Je me suis arrêtée.
+papa|Pieds au bord.
+papa|Sur le trottoir.
+papa|Bravo, Mila.
+narrateur|Le cartable bleu tape encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2046,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2084,6 +2172,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le cartable bleu pend au crochet. La boucle métallique fait un petit clic. Un carré de lumière pose sur le plancher. Il est jaune, un peu poussiéreux. Les chaussures de Mila attendent près du tapis. Le tapis est rêche sous les orteils. Dehors, un merle chante sur le mur. Mila vit ici, avec papa. Papa, le cartable brille ! Oui. On va à l'école. Tu mets tes chaussures ? En ce moment, Mila s'accroupit. Elle enfile la chaussure gauche. Puis la chaussure droite. Tu as fini tes chaussures ? Oui, papa. Bravo. On met le cartable. Papa aide pour la sangle. La sangle est lisse et froide. Papa ouvre la porte. L'air sent le pain de la rue. Ça sent bon ! Oui. On marche sur le trottoir. Mila donne la main à papa. Le cartable tape doucement dans le dos. Le merle chante encore, plus loin. Les pierres du trottoir sont un peu froides. L'école est près ? Bientôt. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris, bien droit. On va s'arrêter. Pieds au bord. Sur le trottoir. Mila s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Parce qu'elle s'arrête, elle attend. Une voiture passe au loin. Mila serre la main de papa. Bravo, Mila. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
+          <t>Le cartable bleu pend au crochet. La boucle métallique fait un petit clic. Un carré de lumière pose sur le plancher. Il est jaune, un peu poussiéreux. Les chaussures de Mila attendent près du tapis. Le tapis est rêche sous les orteils. Dehors, un merle chante sur le mur. Mila vit ici, avec papa. Papa, le cartable brille ! Oui. On va à l'école. Tu mets tes chaussures ? En ce moment, Mila s'accroupit. Elle enfile la chaussure gauche. Puis la chaussure droite. Tu as fini tes chaussures ? Oui, papa. Bravo. On met le cartable. Papa aide pour la sangle. La sangle est lisse et froide. Papa ouvre la porte. L'air sent le pain de la rue. Ça sent bon ! Oui. On marche sur le trottoir. Mila donne la main à papa. Le cartable tape doucement dans le dos. Le merle chante encore, plus loin. Les pierres du trottoir sont un peu froides. L'école est près ? Bientôt. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris, bien droit. On va s'arrêter. Pieds au bord. Sur le trottoir. Mila s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Parce qu'elle s'arrête, elle attend. Une voiture passe au loin. Mila serre la main de papa. Bravo, Mila. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aïcha marche avec papa. Ils vont à l'école. Le cartable est sur son dos. Ils sentent le pain de la rue. Ils arrivent au bord. Le bord du &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt; est là. Papa s'arrête. Aïcha s'arrête aussi. S'arrêter, c'est le geste. Les pieds d'Aïcha sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Papa dit : on s'arrête. Pieds au bord. Sur le trottoir. Aïcha regarde papa. Elle pose les pieds au bord. Les pieds sont calmes. Parce qu'elle s'arrête, elle attend avec papa. Papa sourit. Papa dit : bravo Aïcha. On s'arrête au trottoir. On attend avec papa. Parce que les pieds restent au bord, Aïcha est avec papa. Les pieds restent au bord du trottoir.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le cartable bleu pend au crochet. La boucle métallique fait un petit clic. Un carré de lumière pose sur le plancher. Il est jaune, un peu poussiéreux. Les chaussures de Mila attendent près du tapis. Le tapis est rêche sous les orteils. Dehors, un merle chante sur le mur. Mila vit ici, avec papa. Papa, le cartable brille ! Oui. On va à l'école. Tu mets tes chaussures ? En ce moment, Mila s'accroupit. Elle enfile la chaussure gauche. Puis la chaussure droite. Tu as fini tes chaussures ? Oui, papa. Bravo. On met le cartable. Papa aide pour la sangle. La sangle est lisse et froide. Papa ouvre la porte. L'air sent le pain de la rue. Ça sent bon ! Oui. On marche sur le trottoir. Mila donne la main à papa. Le cartable tape doucement dans le dos. Le merle chante encore, plus loin. Les pierres du trottoir sont un peu froides. L'école est près ? Bientôt. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris, bien droit. On va s'arrêter. Pieds au bord. Sur le trottoir. Mila s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Parce qu'elle s'arrête, elle attend. Une voiture passe au loin. Mila serre la main de papa. Bravo, Mila. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1375,7 +1375,6 @@
 narrateur|Une voiture passe au loin.
 narrateur|Mila serre la main de papa.
 papa|Bravo, Mila.
-papa|Tu as fait du bon travail.
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
@@ -1413,7 +1412,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Aïcha arrive au bord. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1572,7 +1571,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1602,7 +1600,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Aïcha s'arrête au bord. Les pieds sont sur le &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt;. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Mila. On attend avec papa. Parce que les pieds restent au bord, Mila attend. La sangle du cartable est froide. La main de papa est chaude.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1758,7 +1756,6 @@
 narrateur|La main de papa est chaude.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1788,7 +1785,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Aïcha donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à papa. Ils attendent un moment.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On y va ensemble ? Oui, papa. Ils marchent avec l'adulte. Le portail de l'école est bleu. Il sent le métal froid. Tu donnes le cartable ? Mila pousse la sangle. Il est prêt. Tu as fini ? Oui. Bravo. Le merle chante encore sur le mur. Le carré de lumière reste loin, à la maison.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1942,7 +1939,6 @@
 narrateur|Le carré de lumière reste loin, à la maison.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1967,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je me suis arrêtée. Pieds au bord. Sur le trottoir. Bravo, Mila. Le cartable bleu tape encore un peu. L'histoire est finie.</t>
+          <t>Je me suis arrêtée. Pieds au bord. Sur le trottoir. Bravo, Mila. Le cartable bleu tape encore un peu.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je me suis arrêtée. Pieds au bord. Sur le trottoir. Bravo, Mila. Le cartable bleu tape encore un peu.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2111,11 +2107,9 @@
 papa|Pieds au bord.
 papa|Sur le trottoir.
 papa|Bravo, Mila.
-narrateur|Le cartable bleu tape encore un peu.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le cartable bleu tape encore un peu.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2134,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2179,6 +2173,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trajet vers l'école</t>
+          <t>entrée de la maison, trottoir vers l'école</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aïcha, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
